--- a/bq-excel-charts/excel-nativo/Panel_Interactivo.xlsx
+++ b/bq-excel-charts/excel-nativo/Panel_Interactivo.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Verticales</t>
+          <t>Columnas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -686,7 +686,7 @@
       <formula1>=INDIRECT($B$3)</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Verticales,Horizontales"</formula1>
+      <formula1>"Columnas,Barras,Líneas,Área,Circular,Anillo,Radar"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
